--- a/doc/tesztelesek.xlsx
+++ b/doc/tesztelesek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\krivan_balazs\cosmoScreen\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B2389D-5DBB-493A-85DC-05629FEAA010}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DF2C06-1AC3-4B4B-849F-ED2B2159F0AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -139,6 +139,54 @@
   </si>
   <si>
     <t>1.Program elindítása 2.Oldalak megtekintése több méretben</t>
+  </si>
+  <si>
+    <t>Inputok validálása</t>
+  </si>
+  <si>
+    <t>Validáljuk az inputokat az összes oldalon</t>
+  </si>
+  <si>
+    <t>Az inputok megfelelnek a megszabott validációknak</t>
+  </si>
+  <si>
+    <t>Az inputok megfeleltek a megszabott validációknak</t>
+  </si>
+  <si>
+    <t>1.Program elindítása 2.Oldalak megnyitása 3.Inputok teszelése adatokkal</t>
+  </si>
+  <si>
+    <t>Bejelentkezés adatbázisból való történése</t>
+  </si>
+  <si>
+    <t>Ellenőrzi hogy a megadott email-hez tartozó fióknak van e adminisztrátori jogosultsága</t>
+  </si>
+  <si>
+    <t>Az ellenőrzés sikeres így az eredményhez mérten cselekszik a program</t>
+  </si>
+  <si>
+    <t>Sikertelen</t>
+  </si>
+  <si>
+    <t>Helytelen SQL syntax</t>
+  </si>
+  <si>
+    <t>1.Program elindítása  2.Kitölteni a login adatokat 3.Bejelentkezés gomb megnyomása</t>
+  </si>
+  <si>
+    <t>Telepítő teszt</t>
+  </si>
+  <si>
+    <t>A telepítő létrehozza a parancsikont majd kattintásra elindul a program</t>
+  </si>
+  <si>
+    <t>Az alkalmazás sikeresen települt és indítható</t>
+  </si>
+  <si>
+    <t>Az alkalmazás sikeresen települ és indítható</t>
+  </si>
+  <si>
+    <t>1.Telepítő futtatása 2.Program indítása</t>
   </si>
 </sst>
 </file>
@@ -169,15 +217,39 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBAFAF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -185,23 +257,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -209,6 +311,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFBAFAF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -483,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -492,31 +599,32 @@
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -524,51 +632,51 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>45972</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>45974</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -576,51 +684,51 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>45982</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>45987</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -628,51 +736,155 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>45987</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>46002</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46006</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46030</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46036</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>8</v>
       </c>
     </row>

--- a/doc/tesztelesek.xlsx
+++ b/doc/tesztelesek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\krivan_balazs\cosmoScreen\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DF2C06-1AC3-4B4B-849F-ED2B2159F0AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5E78DE-A1AD-4D5C-9AC6-1D483EDCBD9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
